--- a/EXCEL/Exercise Files/Chapter01/01_05_Margin of Error.xlsx
+++ b/EXCEL/Exercise Files/Chapter01/01_05_Margin of Error.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25407"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Curtis\Desktop\Exercise Files\Chapter01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\neha work\Data Analytics\EXCEL\Exercise Files\Chapter01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD37E955-B8E8-429D-A05D-49EAB468C538}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC8547B5-0BCD-40DB-9AE7-6EF1BCB9F3F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="12549" xr2:uid="{7B80CD43-FE4D-4FF0-9E21-B98041C2AC9C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7B80CD43-FE4D-4FF0-9E21-B98041C2AC9C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -69,7 +68,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -141,7 +140,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -169,8 +168,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1814513" cy="353430"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="2" name="TextBox 1">
@@ -217,10 +216,7 @@
               <a:pPr/>
               <a14:m>
                 <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
-                  <m:oMathParaPr>
-                    <m:jc m:val="centerGroup"/>
-                  </m:oMathParaPr>
-                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMath>
                     <m:r>
                       <a:rPr lang="en-US" sz="1200" b="1" i="1">
                         <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
@@ -238,6 +234,7 @@
                         <m:ctrlPr>
                           <a:rPr lang="en-US" sz="1200" b="1" i="1">
                             <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
                           </a:rPr>
                         </m:ctrlPr>
                       </m:fPr>
@@ -280,7 +277,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="2" name="TextBox 1">
@@ -653,26 +650,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C51F496F-61EE-4C0F-AD5E-194C941175E6}">
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.15234375" customWidth="1"/>
-    <col min="2" max="2" width="10.3046875" customWidth="1"/>
+    <col min="1" max="1" width="28.109375" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="16.3828125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.84375" customWidth="1"/>
+    <col min="4" max="4" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="23.15" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:5" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="18.45" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:5" ht="18" x14ac:dyDescent="0.35">
       <c r="D2" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -680,7 +677,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -694,10 +691,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="B5">
+        <v>1.96</v>
+      </c>
       <c r="D5" s="5">
         <v>0.8</v>
       </c>
@@ -705,7 +705,7 @@
         <v>1.28</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
@@ -719,7 +719,7 @@
         <v>1.645</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="2"/>
       <c r="D7" s="5">
         <v>0.95</v>
@@ -728,11 +728,14 @@
         <v>1.96</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="8"/>
+      <c r="B8" s="8">
+        <f>B3/SQRT(B6)</f>
+        <v>1.5811388300841896E-2</v>
+      </c>
       <c r="D8" s="5">
         <v>0.98</v>
       </c>
@@ -740,7 +743,7 @@
         <v>2.33</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D9" s="5">
         <v>0.99</v>
       </c>
@@ -748,11 +751,14 @@
         <v>2.58</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="8"/>
+      <c r="B10" s="8">
+        <f>B5*B8</f>
+        <v>3.0990321069650113E-2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
